--- a/information_forms/023_group_health_plan_billing_information_form--information_forms.xlsx
+++ b/information_forms/023_group_health_plan_billing_information_form--information_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -757,8 +757,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="33" customWidth="1" min="2" max="2"/>
+    <col width="33" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -786,12 +786,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_100,_'label':_'full_coverage'}</t>
+          <t>full_coverage</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 100, 'label': 'Full Coverage'}</t>
+          <t>Full Coverage</t>
         </is>
       </c>
     </row>
@@ -803,12 +803,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_200,_'label':_'partial_coverage'}</t>
+          <t>partial_coverage</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 200, 'label': 'Partial Coverage'}</t>
+          <t>Partial Coverage</t>
         </is>
       </c>
     </row>
@@ -820,12 +820,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_50,_'label':_'ach_(automated_clearing_house)'}</t>
+          <t>ach_(automated_clearing_house)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 50, 'label': 'ACH (Automated Clearing House)'}</t>
+          <t>ACH (Automated Clearing House)</t>
         </is>
       </c>
     </row>
@@ -837,12 +837,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_51,_'label':_'eft_(electronic_funds_transfer)'}</t>
+          <t>eft_(electronic_funds_transfer)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 51, 'label': 'EFT (Electronic Funds Transfer)'}</t>
+          <t>EFT (Electronic Funds Transfer)</t>
         </is>
       </c>
     </row>
@@ -854,12 +854,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_300,_'label':_'immediate'}</t>
+          <t>immediate</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 300, 'label': 'Immediate'}</t>
+          <t>Immediate</t>
         </is>
       </c>
     </row>
@@ -871,12 +871,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_301,_'label':_'30_days'}</t>
+          <t>30_days</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 301, 'label': '30 Days'}</t>
+          <t>30 Days</t>
         </is>
       </c>
     </row>
@@ -888,12 +888,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_302,_'label':_'60_days'}</t>
+          <t>60_days</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 302, 'label': '60 Days'}</t>
+          <t>60 Days</t>
         </is>
       </c>
     </row>
@@ -905,12 +905,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_303,_'label':_'other_(specify)'}</t>
+          <t>other_(specify)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 303, 'label': 'Other (Specify)'}</t>
+          <t>Other (Specify)</t>
         </is>
       </c>
     </row>
